--- a/data/completed_calls.xlsx
+++ b/data/completed_calls.xlsx
@@ -444,7 +444,6 @@
           <t>Snell</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +456,6 @@
           <t>McMurray</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,7 +468,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -478,8 +475,6 @@
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -509,7 +504,6 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,7 +516,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,7 +528,6 @@
           <t>Coggeshall</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,7 +540,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>Snell</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -608,7 +598,6 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -621,7 +610,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -634,7 +622,6 @@
           <t>McMurray</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -647,7 +634,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -660,7 +646,6 @@
           <t>Snell</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -707,7 +692,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -720,7 +704,6 @@
           <t>Thomas</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -733,7 +716,6 @@
           <t>McMurray</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -746,7 +728,6 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -759,7 +740,6 @@
           <t>Wallace</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -806,7 +786,6 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -819,7 +798,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -832,7 +810,6 @@
           <t>McMurray</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -845,7 +822,6 @@
           <t>Thomas</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -858,7 +834,6 @@
           <t>Coggeshall</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -905,7 +880,6 @@
           <t>Hall</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -918,7 +892,6 @@
           <t>Davis</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -931,7 +904,6 @@
           <t>Schaeffer</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -944,7 +916,6 @@
           <t>Hall</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -957,7 +928,6 @@
           <t>Davis</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -989,7 +959,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Loera</t>
         </is>
       </c>
     </row>
@@ -1004,7 +974,6 @@
           <t>Davis</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1017,7 +986,6 @@
           <t>Schaeffer</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1030,7 +998,6 @@
           <t>Hall</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1043,7 +1010,6 @@
           <t>Wallace</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1056,7 +1022,6 @@
           <t>Schaeffer</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1103,7 +1068,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1116,7 +1080,6 @@
           <t>Schaeffer</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1129,7 +1092,6 @@
           <t>Hall</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1142,7 +1104,6 @@
           <t>Davis</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1155,7 +1116,6 @@
           <t>Wallace</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1202,7 +1162,6 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1215,7 +1174,6 @@
           <t>Schaeffer</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1228,7 +1186,6 @@
           <t>Hall</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1241,7 +1198,6 @@
           <t>Davis</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1254,7 +1210,6 @@
           <t>Wallace</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1298,10 +1253,9 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Prahbu</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Prabhu</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1314,7 +1268,6 @@
           <t>Thomas</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1327,7 +1280,6 @@
           <t>Snell</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1337,10 +1289,9 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Prahbu</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>Prabhu</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1353,7 +1304,6 @@
           <t>Riaz</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1380,7 +1330,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Prahbu</t>
+          <t>Prabhu</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1395,8 +1345,6 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1409,7 +1357,6 @@
           <t>Riaz</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1419,10 +1366,9 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Prahbu</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Prabhu</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1435,7 +1381,6 @@
           <t>Snell</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1448,7 +1393,6 @@
           <t>Riaz</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1475,7 +1419,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prahbu</t>
+          <t>Prabhu</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1495,7 +1439,6 @@
           <t>Coggeshall</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1508,7 +1451,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1518,10 +1460,9 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Prahbu</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Prabhu</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1534,7 +1475,6 @@
           <t>Thomas</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1547,7 +1487,6 @@
           <t>Riaz</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1591,10 +1530,9 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Prahbu</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>Prabhu</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1607,7 +1545,6 @@
           <t>Wallace</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1620,7 +1557,6 @@
           <t>Coggeshall</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1633,7 +1569,6 @@
           <t>Snell</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1646,7 +1581,6 @@
           <t>Thomas</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1693,7 +1627,6 @@
           <t>Fuentes</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1706,7 +1639,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1719,7 +1651,6 @@
           <t>McMurray</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1732,7 +1663,6 @@
           <t>Fuentes</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1745,7 +1675,6 @@
           <t>Schaeffer</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1777,7 +1706,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Loera</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1721,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1805,7 +1733,6 @@
           <t>Coggeshall</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1818,7 +1745,6 @@
           <t>Fuentes</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1831,7 +1757,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1844,7 +1769,6 @@
           <t>McMurray</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1891,7 +1815,6 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1904,7 +1827,6 @@
           <t>Riaz</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1917,7 +1839,6 @@
           <t>Fuentes</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1930,7 +1851,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1943,7 +1863,6 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1990,7 +1909,6 @@
           <t>Fuentes</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2003,7 +1921,6 @@
           <t>Schaeffer</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2016,7 +1933,6 @@
           <t>Coggeshall</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2029,7 +1945,6 @@
           <t>Fuentes</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2042,7 +1957,6 @@
           <t>Clark</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2057,7 +1971,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Loera</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2003,6 @@
           <t>Davis</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2102,7 +2015,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2115,7 +2027,6 @@
           <t>Snell</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2128,7 +2039,6 @@
           <t>Wallace</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2141,7 +2051,6 @@
           <t>Schaeffer</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2188,7 +2097,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2201,7 +2109,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2214,7 +2121,6 @@
           <t>Davis</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2227,7 +2133,6 @@
           <t>Snell</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2240,7 +2145,6 @@
           <t>Wallace</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2255,7 +2159,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avila</t>
+          <t>Loera</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2191,6 @@
           <t>Behaj</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2300,7 +2203,6 @@
           <t>Green</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2313,7 +2215,6 @@
           <t>Davis</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2326,7 +2227,6 @@
           <t>Coggeshall</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2339,7 +2239,6 @@
           <t>Wallace</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
